--- a/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
+++ b/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
@@ -396,7 +396,7 @@
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">LIMITED PASS</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -406,7 +406,7 @@
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 400; /v1/mau/batches</t>
+          <t xml:space="preserve">HTTP 400; /v1/mau/batches; empty payload rejected; does not establish rejection of a structurally valid unsigned request</t>
         </is>
       </c>
     </row>
@@ -418,7 +418,7 @@
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">LIMITED PASS</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -428,7 +428,7 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 400; /v1/revenue/batches</t>
+          <t xml:space="preserve">HTTP 400; /v1/revenue/batches; empty payload rejected; does not establish rejection of a structurally valid unsigned request</t>
         </is>
       </c>
     </row>
@@ -440,7 +440,7 @@
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">PASS</t>
+          <t xml:space="preserve">LIMITED PASS</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -450,7 +450,7 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTTP 400; /v1/deployments/register</t>
+          <t xml:space="preserve">HTTP 400; /v1/deployments/register; empty payload rejected; does not establish rejection of a structurally valid unsigned request</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -799,14 +799,65 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MinIO seed before / after</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23.771s / 2.157s</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isolated owned bucket; component benchmark, source fix not yet installed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JVM periodic GC trial RSS</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">574.94MiB / 575.06MiB</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">85s experiment, original flag restored; no improvement</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JVM committed heap</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271MiB</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reserved maximum ~1.31GiB is not actual resident usage</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C13"/>
+  <autoFilter ref="A1:C16"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -877,7 +928,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">INVESTIGATE</t>
+          <t xml:space="preserve">COMPONENT FIX VERIFIED / STACK RETEST PENDING</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -887,12 +938,12 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warm start 77.85s; isolate JVM initialization and health polling before changing runtime.</t>
+          <t xml:space="preserve">MinIO seed process batching: 23.771s to 2.157s (90.9% faster), identical 879-object inventory and MIME types. Source fix only; installed image unchanged. Health start_interval source change also pending packaged qualification.</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">runtime-20260916.json</t>
+          <t xml:space="preserve">minio-seed-20260916.json; full stack baseline remains 77.85s</t>
         </is>
       </c>
     </row>
@@ -923,7 +974,115 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEM-001</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEASURED / NO TUNING RETAINED</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G1 periodic concurrent collection trial (30s interval): committed heap stayed 271MiB; RSS 574.94 to 575.06MiB, no material reduction. Original interval 0 restored and verified. Do not ship this tuning as an optimization. Live browser activity was not controlled.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">idle-heap-20260916.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MEM-002</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ATTRIBUTED / LOAD TEST PENDING</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post-seed API RSS 551.4MiB; Mongo live cache ~20.4MiB despite configured maximum ~2.1GiB. No measured justification for arbitrary heap/cache caps. No OOM observed; sustained load/leak behavior remains unproven.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">memory-after-seed-20260916.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REL-001</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPEN</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Real Registry reports dev, not a stable release version. Qualify and stamp the actual Registry release before release evidence is final.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Registry version observed during qualification; independent from TLS retest</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI-001</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOURCE FIX / VM RETEST PENDING</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When native permission is granted, save the browser preference immediately and register FCM in the background. Settings popup remains open after Update; login permission gate still closes on completion. Switch reflects saved preference, not token registration completion. Technical waits capped at 3s each; native decision is not timed out. VM still runs older frontend.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firebase-messaging.service.spec.ts; server Firebase configuration HTTP200 in37ms; live user browser flow not automated</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E8"/>
 </worksheet>
 </file>
--- a/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
+++ b/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
@@ -1073,12 +1073,12 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">When native permission is granted, save the browser preference immediately and register FCM in the background. Settings popup remains open after Update; login permission gate still closes on completion. Switch reflects saved preference, not token registration completion. Technical waits capped at 3s each; native decision is not timed out. VM still runs older frontend.</t>
+          <t xml:space="preserve">When native permission is granted, save the browser preference immediately and register FCM in the background. Settings popup remains open after Update; login permission gate still closes on completion. Switch reflects saved preference, not token registration completion. Backend device writes capped at 3s; initial FCM token setup runs in the background with a 30s bound; native decision is not timed out. VM still runs older frontend. Granted geolocation is now synchronized in the background on Settings Update as well; a failed first save does not mark optimistic coordinates as persisted, allowing a later retry. r2 preloads the Messaging configuration before the explicit native-permission click and skips native/token work when unconfigured. Opt-out writes backend removal without waiting for Firebase.</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">firebase-messaging.service.spec.ts; server Firebase configuration HTTP200 in37ms; live user browser flow not automated</t>
+          <t xml:space="preserve">54 focused tests PASS (13 messaging, 4 location, 37 HTTP Operator Registry); production r2 frontend and seed/i18n gates passed; QA3 replacement packaging in progress; real member notification delivery remains unproven.</t>
         </is>
       </c>
     </row>

--- a/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
+++ b/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
@@ -1078,7 +1078,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">54 focused tests PASS (13 messaging, 4 location, 37 HTTP Operator Registry); production r2 frontend and seed/i18n gates passed; QA3 replacement packaging in progress; real member notification delivery remains unproven.</t>
+          <t xml:space="preserve">57 focused tests PASS (13 messaging, 4 location, 40 HTTP Operator Registry); production r4 frontend and seed/i18n gates passed; signed QA3 r4 served on local HTTPS; VM catalog and streamed artifact hash verified; user-operated update pending. Runtime VAPID is loaded from server Operator configuration; missing runtime renders Notifications OFF/disabled. Real member notification delivery and installed QA3 behavior remain unproven.</t>
         </is>
       </c>
     </row>

--- a/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
+++ b/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
@@ -6,6 +6,9 @@
     <sheet name="Security" sheetId="2" r:id="rId2"/>
     <sheet name="Runtime" sheetId="3" r:id="rId3"/>
     <sheet name="Findings" sheetId="4" r:id="rId4"/>
+    <sheet name="Current QA3" sheetId="5" r:id="rId5"/>
+    <sheet name="Current security" sheetId="6" r:id="rId6"/>
+    <sheet name="Reduction candidates" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -88,12 +91,12 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA2 monitor-r8</t>
+          <t xml:space="preserve">1.0.0-qa.3 / permission-sync-r4</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHA256 29c404680876568dbd7d40fd4b85422acc8e59e4f2824feb24ff662eb4203444</t>
+          <t xml:space="preserve">Verified live /app-version.json at 2026-09-16 22:24 local; no rebuild or restart in this review. Historical Runtime sheet retained as earlier QA2 baseline.</t>
         </is>
       </c>
     </row>
@@ -928,7 +931,7 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMPONENT FIX VERIFIED / STACK RETEST PENDING</t>
+          <t xml:space="preserve">INSTALLED / STARTUP OBSERVED</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -938,7 +941,7 @@
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">MinIO seed process batching: 23.771s to 2.157s (90.9% faster), identical 879-object inventory and MIME types. Source fix only; installed image unchanged. Health start_interval source change also pending packaged qualification.</t>
+          <t xml:space="preserve">Batched MinIO seed is present in running QA3 r4. Current startup-to-seed-complete 4.793s includes waiting for MinIO; earlier isolated23.771s/2.157s comparison is a different benchmark. Full stack restart not replayed.</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
@@ -1063,7 +1066,7 @@
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOURCE FIX / VM RETEST PENDING</t>
+          <t xml:space="preserve">SUPERSEDED SOURCE DESCRIPTION</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -1073,7 +1076,7 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">When native permission is granted, save the browser preference immediately and register FCM in the background. Settings popup remains open after Update; login permission gate still closes on completion. Switch reflects saved preference, not token registration completion. Backend device writes capped at 3s; initial FCM token setup runs in the background with a 30s bound; native decision is not timed out. VM still runs older frontend. Granted geolocation is now synchronized in the background on Settings Update as well; a failed first save does not mark optimistic coordinates as persisted, allowing a later retry. r2 preloads the Messaging configuration before the explicit native-permission click and skips native/token work when unconfigured. Opt-out writes backend removal without waiting for Firebase.</t>
+          <t xml:space="preserve">Earlier background-save description is superseded by user corrections. Current source now waits for registration result; running r4 is unchanged. See permission evidence and current source tests; no new live notification PASS.</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -1085,4 +1088,830 @@
   </sheetData>
   <autoFilter ref="A1:E8"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C14"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measurement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence / limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identity</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">qa3-20260916-permission-sync-r4</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">http-current-20260916-2225.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VM available RAM</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.40 GiB of 5.24 GiB</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 samples; no swap; memory pressure avg10/60/300=0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All 9 containers working set</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1097.4–1098.2 MiB</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Short observation, not a leak or load test</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java API working set</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">644.5–644.6 MiB</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Process RSS 641.49 MiB; 65 threads</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JVM heap</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254 MiB used / 319 MiB committed</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maximum 1342 MiB is not actual RSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MongoDB</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247.4–247.7 MiB</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WiredTiger live cache 46.43 MiB / configured max 2168 MiB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MinIO</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145.5–145.7 MiB</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Batched copy installed; startup-to-seed-complete 4.793s from existing logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spring startup</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11.527 s</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing current-container log, not new full-stack restart</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP public configuration</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10.2–18.0 ms</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 workstation-to-localhost-tunnel requests, no browser rendering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9/9 healthy; 0 OOM / restarts reported</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Current containers only, not historical host OOM proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security probes</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 PASS + 3 LIMITED PASS</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18 expected responses; unsigned Registry tests use empty bodies only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">External ports</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22,80,443,18082,18444</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18082 returns 308 redirect to Registry HTTPS; internal DB/cache/media/API unreachable from workstation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changes made to running stack</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read-only diagnostics; no runtime flags, restarts, installs or database changes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C14"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C23"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Result</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence / scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-ANON-configuration</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 403; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-ANON-tls</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 403; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-ANON-updates</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 403; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-INVALID-TOKEN</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 401; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-EXPOSURE-/.env</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 200; No sensitive file returned; SPA shell200 is not file disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-EXPOSURE-/.git/config</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 200; No sensitive file returned; SPA shell200 is not file disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-EXPOSURE-/actuator/env</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 200; No sensitive file returned; SPA shell200 is not file disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="65" customHeight="1">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-EXPOSURE-/actuator/heapdump</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 200; No sensitive file returned; SPA shell200 is not file disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="65" customHeight="1">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-EXPOSURE-/api/actuator/env</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 403; No sensitive file returned; SPA shell200 is not file disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="65" customHeight="1">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">APP-EXPOSURE-/api/actuator/heapdump</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 403; No sensitive file returned; SPA shell200 is not file disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="65" customHeight="1">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG-UNSIGNED-/v1/mau/batches</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMITED PASS</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 400; empty body rejection does not prove valid unsigned rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG-UNSIGNED-/v1/revenue/batches</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMITED PASS</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 400; empty body rejection does not prove valid unsigned rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG-UNSIGNED-/v1/deployments/register</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIMITED PASS</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 400; empty body rejection does not prove valid unsigned rejection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="65" customHeight="1">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG-CANONICAL-PATH</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 400; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG-EXPOSURE-/.env</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 404; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG-EXPOSURE-/.git/config</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 404; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="65" customHeight="1">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG-EXPOSURE-/debug/pprof/</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 404; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="65" customHeight="1">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REG-EXPOSURE-/metrics</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTTP 404; bounded negative probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="65" customHeight="1">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPA response headers</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GAP</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HSTS present; CSP, X-Frame-Options, nosniff, Referrer-Policy absent on /. API headers do not cover frontend HTML.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="65" customHeight="1">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Container isolation</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PARTIAL</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No privileged containers; API user 10001. API lacks no-new-privileges/read-only-root settings used by Registry and simulator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="65" customHeight="1">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">App / external Registry networks</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">server_myscoutee separate from myscoutee-registry_internal/public (see runtime evidence for exact names).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="65" customHeight="1">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOT RUN</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cross-account/role flows, upload exploit paths, signed replay, dependency/container CVEs, Internet perimeter. No claim of complete security qualification.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C23"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D7"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decision</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Measured basis / tradeoff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primary source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Java 25 AOT cache / extracted application</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First candidate; not implemented</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Targets startup/class loading and memory; actual savings not measured. Rebuild cache for changed app/JDK; controlled training needed.</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://docs.spring.io/spring-boot/reference/packaging/aot-cache.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heap sizing / free-space ratios</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary; no arbitrary cap applied</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heap 254 used /319 committed; 1342 maximum is only limit. Smaller heap may increase GC work.</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://docs.oracle.com/en/java/javase/25/gctuning/factors-affecting-garbage-collection-performance.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mongo cache cap</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not an immediate saving</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only46.43 MiB currently used. Limit is capacity protection, not equivalent RSS reduction.</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.mongodb.com/docs/v8.0/core/wiredtiger/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Global Spring lazy initialization</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not selected</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moves initialization/failures to first request; does not establish durable memory savings.</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://docs.spring.io/spring-boot/reference/features/spring-application.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SPA security headers</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open hardening change</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Add framing and nosniff/referrer protection; evaluate CSP in report-only mode first to preserve Firebase/media integration.</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://developer.mozilla.org/en-US/docs/Web/HTTP/Headers/Content-Security-Policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">API container hardening</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open candidate</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluate no-new-privileges and capability removal; verify required writable paths before read-only root.</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://docs.docker.com/engine/security/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D7"/>
+</worksheet>
 </file>
--- a/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
+++ b/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Current QA3" sheetId="5" r:id="rId5"/>
     <sheet name="Current security" sheetId="6" r:id="rId6"/>
     <sheet name="Reduction candidates" sheetId="7" r:id="rId7"/>
+    <sheet name="Security fixes" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -1914,4 +1915,173 @@
   </sheetData>
   <autoFilter ref="A1:D7"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:D7"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source change</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verification</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deployment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="65" customHeight="1">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production response headers</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added nosniff, DENY, strict-origin-when-cross-origin and CSP frame-ancestors/object-src/base-uri</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">packaging/tests/nginx-transport-policy-test.sh PASS, root + JS + manifest headers</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not deployed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="65" customHeight="1">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend runtime dependencies</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Angular 21.2.23, grpc-js 1.9.16, protobufjs 7.6.6, websocket-driver 0.7.5</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">npm audit --omit=dev: 9 to 0 findings; 22 focused Angular tests passed</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not deployed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Firebase-disabled production identity</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An empty production member-user disables userId-based identity fallback and retains authenticated policy checks</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New MockMvc regression PASS with/without bootstrap; local/demo tests PASS</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not deployed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Security regression suite</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selected filter, routing, policy, media and bootstrap tests</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110/111 PASS; releasedFormerOwnerCannotRetakeOrMutateTheAssetAsOwner remains FAIL at delete assertion; no full security sign-off</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not deployed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="65" customHeight="1">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Backend dependencies</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inventory only: embedded Maven metadata from previously built local JAR</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSV findings still open; scan does not include JARs without Maven metadata or prove live exploitability</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No backend dependency changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notification save error</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Keep user-selected toggle on save failure and show existing translated error; retry without toggling</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22/22 focused tests PASS; waits for server acknowledgment before success</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not deployed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D7"/>
+</worksheet>
 </file>
--- a/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
+++ b/guides/qualification/SECURITY_AND_INFRASTRUCTURE.xlsx
@@ -131,7 +131,7 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Finite negative probes; authenticated cross-account, upload, replay and CVE checks not yet performed.</t>
+          <t xml:space="preserve">Finite live negative probes and source-level security regression checks. Runtime dependency audits have zero findings after source fixes. Live authenticated cross-account retest of the new artifact is not run.</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">110/111 PASS; releasedFormerOwnerCannotRetakeOrMutateTheAssetAsOwner remains FAIL at delete assertion; no full security sign-off</t>
+          <t xml:space="preserve">114/114 PASS: bootstrap/filter/routing/media/policy/identity checks. Includes cross-account asset mutation, released owner and missing authenticated profile. Mocked repositories; not a live full-application security certification.</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inventory only: embedded Maven metadata from previously built local JAR</t>
+          <t xml:space="preserve">Spring Boot 4.0.8; jsoup 1.23.1; iText 5.5.13.3; HttpClient5 5.6.3; HttpCore5 5.4.3; Tomcat 11.0.25; OpenTelemetry 1.62.0</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSV findings still open; scan does not include JARs without Maven metadata or prove live exploitability</t>
+          <t xml:space="preserve">OSV querybatch: 263 resolved runtimeClasspath coordinates, 0 findings. Focused backend compile/tests PASS. Earlier partial JAR inventory retained as historical evidence.</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">No backend dependency changes</t>
+          <t xml:space="preserve">Not deployed</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,29 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="65" customHeight="1">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cross-account ownership</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Existing asset edit/delete/restore checks stored, non-released ownership. Authenticated profile lookup cannot fall back to a caller-selected account.</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New regression cases PASS; previous released-owner case now PASS. No live data mutated.</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not deployed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D8"/>
 </worksheet>
 </file>